--- a/Config/Datas/h_act_info.xlsx
+++ b/Config/Datas/h_act_info.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>player_min_desire</t>
   </si>
   <si>
+    <t>is_player_passive</t>
+  </si>
+  <si>
     <t>h_impulse_base</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>玩家欲望要求</t>
   </si>
   <si>
+    <t>主角被动？</t>
+  </si>
+  <si>
     <t>h冲击力</t>
   </si>
   <si>
@@ -95,6 +104,9 @@
   </si>
   <si>
     <t>Static</t>
+  </si>
+  <si>
+    <t>FALSE</t>
   </si>
   <si>
     <t>10</t>
@@ -1058,13 +1070,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="9" width="9" style="1"/>
+    <col min="2" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1092,68 +1104,77 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
@@ -1162,55 +1183,59 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="1">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1219,22 +1244,24 @@
         <v>25</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1243,68 +1270,76 @@
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="1">
+        <v>27</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1313,21 +1348,24 @@
         <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -1336,36 +1374,42 @@
         <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/h_act_info.xlsx
+++ b/Config/Datas/h_act_info.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -40,7 +40,7 @@
     <t>desc</t>
   </si>
   <si>
-    <t>filter_type</t>
+    <t>filter_types</t>
   </si>
   <si>
     <t>player_min_desire</t>
@@ -70,6 +70,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=;),string</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -137,6 +140,36 @@
   </si>
   <si>
     <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>KaiYou</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
 </sst>
 </file>
@@ -752,12 +785,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1070,13 +1106,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="10" width="9" style="1"/>
+    <col min="2" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="22.875" style="1" customWidth="1"/>
+    <col min="5" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1108,7 +1146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1118,63 +1156,63 @@
       <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
@@ -1183,233 +1221,418 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:18">
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:18">
       <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>28</v>
+      <c r="H13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/h_act_info.xlsx
+++ b/Config/Datas/h_act_info.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t>17</t>
+  </si>
+  <si>
+    <t>Simple</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="9" style="1"/>
@@ -1632,6 +1638,52 @@
         <v>28</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>29</v>
       </c>
     </row>

--- a/Config/Datas/h_act_info.xlsx
+++ b/Config/Datas/h_act_info.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="113">
   <si>
     <t>##var</t>
   </si>
@@ -106,7 +106,13 @@
     <t>高潮比例</t>
   </si>
   <si>
-    <t>Static</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>对倒地手榨</t>
+  </si>
+  <si>
+    <t>Unsensor</t>
   </si>
   <si>
     <t>FALSE</t>
@@ -118,64 +124,250 @@
     <t>0</t>
   </si>
   <si>
-    <t>1</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>对倒地手口</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>对倒地口</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>对倒地乳</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>对倒地口乳</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>对倒地素股</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>对倒地骑乘插入</t>
+  </si>
+  <si>
+    <t>吻封坐屌</t>
+  </si>
+  <si>
+    <t>FemaleForce</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>骑乘塞乳</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>坐脸反身踩J</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>逆传教士</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>正面拥吻</t>
+  </si>
+  <si>
+    <t>Charmed</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>背后揉胸吻</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>按头口爆</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>抬腿扣咬乳</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>简单69</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>抱起温柔入</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Charmed</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>扶墙温柔后入</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>抬腿温柔站入</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>强化抱起入</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>强化扶墙后入</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>被摸胸</t>
   </si>
   <si>
     <t>KaiYou</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>被强吻</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>被拍屁股</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>被扣扣</t>
+  </si>
+  <si>
+    <t>被舔穴</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>擦枪</t>
+  </si>
+  <si>
+    <t>洗面奶</t>
+  </si>
+  <si>
+    <t>QuickStand</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>强吻摩擦</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>舔脖子+手撸</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>正常体位</t>
+  </si>
+  <si>
+    <t>KnockDown</t>
   </si>
   <si>
     <t>True</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Simple</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>51</t>
+  </si>
+  <si>
+    <t>正常后入</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>正常侧入</t>
+  </si>
+  <si>
+    <t>蹂躏踩屌</t>
+  </si>
+  <si>
+    <t>Conquer</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>蹂躏舔脚</t>
   </si>
 </sst>
 </file>
@@ -1112,15 +1304,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="3" width="9" style="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.875" style="1" customWidth="1"/>
-    <col min="5" max="10" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
+    <col min="7" max="10" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1152,7 +1347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1184,7 +1379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1216,7 +1411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1248,443 +1443,987 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
-      <c r="B5" s="1">
-        <v>1</v>
+    <row r="5" spans="1:10">
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
-      <c r="B6" s="1">
-        <v>2</v>
+    <row r="6" spans="1:10">
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:10">
+      <c r="B13" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="B7" s="1">
+      <c r="C13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:10">
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:10">
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:10">
+      <c r="B16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
+      <c r="B18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
+      <c r="B21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
+      <c r="B22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
+      <c r="B23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
+      <c r="B24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="B25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="B26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="B27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="B29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="H29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R29" s="2"/>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="H30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="B31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="B11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="1">
-        <v>3</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="B13" s="1" t="s">
+      <c r="H31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="B32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="2"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>29</v>
+      <c r="H32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
